--- a/CDF_Lid_Tolerance/SplineCDF_Fall2025_Lid Mat Cost.xlsx
+++ b/CDF_Lid_Tolerance/SplineCDF_Fall2025_Lid Mat Cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF_Lid_Tolerance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545E635C-8E76-4E81-96AA-7CE204948167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{545E635C-8E76-4E81-96AA-7CE204948167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D27E76FE-E280-4819-8119-1AA05698D1DA}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6541,127 +6541,127 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>1</v>
+        <v>0.45128015750607797</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>1.2</v>
+        <v>0.49121185088097918</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <f ca="1">INDIRECT("Computations!B"&amp;C2)</f>
-        <v>1</v>
+        <v>0.49000000000000005</v>
       </c>
       <c r="E2">
         <f ca="1">INDIRECT("Computations!B"&amp;(C2+1))</f>
-        <v>1.2</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F2">
         <f ca="1">INDIRECT("Computations!S"&amp;C2)</f>
-        <v>-4.1176470588235259E-2</v>
+        <v>3.6538461538461492E-2</v>
       </c>
       <c r="G2">
         <f ca="1">INDIRECT("Computations!R"&amp;C2)</f>
-        <v>-1.764705882352946E-2</v>
+        <v>-6.1538461538461486E-2</v>
       </c>
       <c r="H2">
         <f ca="1">INDIRECT("Computations!Q"&amp;C2)</f>
-        <v>0.1588235294117647</v>
+        <v>7.4999999999999983E-2</v>
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-9.9999999999999978E-2</v>
+        <v>-1.2801575060779613E-3</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>0.62962962962962954</v>
+        <v>1.7068766747706153E-2</v>
       </c>
       <c r="K2">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>0.68118692087013366</v>
+        <v>1.7314757160444741E-2</v>
       </c>
       <c r="L2">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>0.68118692087013366</v>
+        <v>1.7314757160444741E-2</v>
       </c>
       <c r="M2">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
-        <v>-3.918367346938779</v>
+        <v>1.1071098799630668</v>
       </c>
       <c r="N2">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>2.9854227405247853</v>
+        <v>0.7634392147105693</v>
       </c>
       <c r="O2">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>0</v>
-      </c>
-      <c r="P2">
+        <v>0.19596823049022655</v>
+      </c>
+      <c r="P2" t="e">
         <f ca="1">SQRT(N2^2/4-O2)</f>
-        <v>1.4927113702623926</v>
-      </c>
-      <c r="Q2">
+        <v>#NUM!</v>
+      </c>
+      <c r="Q2" t="e">
         <f ca="1">P2^(1/3)</f>
-        <v>1.1428571428571435</v>
-      </c>
-      <c r="R2">
+        <v>#NUM!</v>
+      </c>
+      <c r="R2" t="e">
         <f ca="1">ACOS(-N2/2/P2)</f>
-        <v>3.1415926535897931</v>
-      </c>
-      <c r="S2">
+        <v>#NUM!</v>
+      </c>
+      <c r="S2" t="e">
         <f ca="1">-Q2</f>
-        <v>-1.1428571428571435</v>
-      </c>
-      <c r="T2">
+        <v>#NUM!</v>
+      </c>
+      <c r="T2" t="e">
         <f ca="1">COS(R2/3)</f>
-        <v>0.50000000000000011</v>
-      </c>
-      <c r="U2">
+        <v>#NUM!</v>
+      </c>
+      <c r="U2" t="e">
         <f ca="1">SQRT(3)*SIN(R2/3)</f>
-        <v>1.4999999999999998</v>
+        <v>#NUM!</v>
       </c>
       <c r="V2">
         <f ca="1">-G2/F2/3</f>
-        <v>-0.14285714285714338</v>
-      </c>
-      <c r="W2">
+        <v>0.56140350877193013</v>
+      </c>
+      <c r="W2" t="e">
         <f ca="1">2*Q2*T2+V2</f>
-        <v>1.0000000000000002</v>
-      </c>
-      <c r="X2">
+        <v>#NUM!</v>
+      </c>
+      <c r="X2" t="e">
         <f ca="1">S2*(T2+U2)+V2</f>
-        <v>-2.4285714285714302</v>
-      </c>
-      <c r="Y2">
+        <v>#NUM!</v>
+      </c>
+      <c r="Y2" t="e">
         <f ca="1">S2*(T2-U2)+V2</f>
-        <v>0.99999999999999967</v>
+        <v>#NUM!</v>
       </c>
       <c r="Z2">
         <f ca="1">-N2/2+SQRT(O2)</f>
-        <v>-1.4927113702623926</v>
+        <v>6.0963383610289412E-2</v>
       </c>
       <c r="AA2">
         <f ca="1">Z2^(1/3)</f>
-        <v>-1.1428571428571435</v>
+        <v>0.39357093734543847</v>
       </c>
       <c r="AB2">
         <f ca="1">-N2/2-SQRT(O2)</f>
-        <v>-1.4927113702623926</v>
+        <v>-0.82440259832085871</v>
       </c>
       <c r="AC2">
         <f ca="1">AB2^(1/3)</f>
-        <v>-1.1428571428571435</v>
+        <v>-0.93766229067480911</v>
       </c>
       <c r="AD2">
         <f ca="1">AA2+AC2+V2</f>
-        <v>-2.4285714285714302</v>
+        <v>1.7312155442559485E-2</v>
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>1.0000000000000002</v>
+        <v>1.7312155442559485E-2</v>
       </c>
       <c r="AG2" t="s">
         <v>58</v>
@@ -36495,15 +36495,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010000B92449D07C8D4B9A11B36D3DD1493B" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="12876fd8bd5d90ce750491db8e9e67c2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18b8549e-3e0d-4ec5-af2b-e3bc54260487" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="45151d2993f903c2059e1e395416a0b1" ns2:_="">
     <xsd:import namespace="18b8549e-3e0d-4ec5-af2b-e3bc54260487"/>
@@ -36641,6 +36632,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -36648,14 +36648,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00701729-9E26-45E2-A33F-8BB46F87F68B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3ABAFEA-1016-4C54-A559-F808DE7BB270}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36673,6 +36665,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00701729-9E26-45E2-A33F-8BB46F87F68B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EF0FBCC-E871-4949-A77D-1C46D5FD7A0C}">
   <ds:schemaRefs>

--- a/CDF_Lid_Tolerance/SplineCDF_Fall2025_Lid Mat Cost.xlsx
+++ b/CDF_Lid_Tolerance/SplineCDF_Fall2025_Lid Mat Cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF_Lid_Tolerance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{545E635C-8E76-4E81-96AA-7CE204948167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D27E76FE-E280-4819-8119-1AA05698D1DA}"/>
+  <xr:revisionPtr revIDLastSave="354" documentId="13_ncr:1_{545E635C-8E76-4E81-96AA-7CE204948167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{886A31E0-1E34-4810-9603-5CE0FF79E901}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4779,6 +4779,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6541,63 +6545,63 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>0.45128015750607797</v>
+        <v>0.29224228801401098</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>0.49121185088097918</v>
+        <v>0.41329796036377697</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <f ca="1">INDIRECT("Computations!B"&amp;C2)</f>
-        <v>0.49000000000000005</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="E2">
         <f ca="1">INDIRECT("Computations!B"&amp;(C2+1))</f>
-        <v>0.56000000000000005</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="F2">
         <f ca="1">INDIRECT("Computations!S"&amp;C2)</f>
-        <v>3.6538461538461492E-2</v>
+        <v>2.5714285714285717E-2</v>
       </c>
       <c r="G2">
         <f ca="1">INDIRECT("Computations!R"&amp;C2)</f>
-        <v>-6.1538461538461486E-2</v>
+        <v>-2.5714285714285717E-2</v>
       </c>
       <c r="H2">
         <f ca="1">INDIRECT("Computations!Q"&amp;C2)</f>
-        <v>7.4999999999999983E-2</v>
+        <v>0.06</v>
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-1.2801575060779613E-3</v>
+        <v>-5.2242288014010985E-2</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>1.7068766747706153E-2</v>
-      </c>
-      <c r="K2">
+        <v>0.87070480023351648</v>
+      </c>
+      <c r="K2" t="e">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>1.7314757160444741E-2</v>
-      </c>
-      <c r="L2">
+        <v>#NUM!</v>
+      </c>
+      <c r="L2" t="e">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>1.7314757160444741E-2</v>
+        <v>#NUM!</v>
       </c>
       <c r="M2">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
-        <v>1.1071098799630668</v>
+        <v>1.9999999999999998</v>
       </c>
       <c r="N2">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>0.7634392147105693</v>
+        <v>-1.327940830174501</v>
       </c>
       <c r="O2">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>0.19596823049022655</v>
+        <v>0.73715300840743203</v>
       </c>
       <c r="P2" t="e">
         <f ca="1">SQRT(N2^2/4-O2)</f>
@@ -6625,7 +6629,7 @@
       </c>
       <c r="V2">
         <f ca="1">-G2/F2/3</f>
-        <v>0.56140350877193013</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="W2" t="e">
         <f ca="1">2*Q2*T2+V2</f>
@@ -6641,27 +6645,27 @@
       </c>
       <c r="Z2">
         <f ca="1">-N2/2+SQRT(O2)</f>
-        <v>6.0963383610289412E-2</v>
+        <v>1.5225465668684608</v>
       </c>
       <c r="AA2">
         <f ca="1">Z2^(1/3)</f>
-        <v>0.39357093734543847</v>
+        <v>1.1504211606416055</v>
       </c>
       <c r="AB2">
         <f ca="1">-N2/2-SQRT(O2)</f>
-        <v>-0.82440259832085871</v>
+        <v>-0.19460573669395986</v>
       </c>
       <c r="AC2">
         <f ca="1">AB2^(1/3)</f>
-        <v>-0.93766229067480911</v>
+        <v>-0.57949791734955358</v>
       </c>
       <c r="AD2">
         <f ca="1">AA2+AC2+V2</f>
-        <v>1.7312155442559485E-2</v>
+        <v>0.90425657662538517</v>
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>1.7312155442559485E-2</v>
+        <v>0.90425657662538517</v>
       </c>
       <c r="AG2" t="s">
         <v>58</v>
@@ -36495,6 +36499,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010000B92449D07C8D4B9A11B36D3DD1493B" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="12876fd8bd5d90ce750491db8e9e67c2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18b8549e-3e0d-4ec5-af2b-e3bc54260487" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="45151d2993f903c2059e1e395416a0b1" ns2:_="">
     <xsd:import namespace="18b8549e-3e0d-4ec5-af2b-e3bc54260487"/>
@@ -36632,15 +36645,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -36648,6 +36652,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00701729-9E26-45E2-A33F-8BB46F87F68B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3ABAFEA-1016-4C54-A559-F808DE7BB270}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36665,14 +36677,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00701729-9E26-45E2-A33F-8BB46F87F68B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EF0FBCC-E871-4949-A77D-1C46D5FD7A0C}">
   <ds:schemaRefs>

--- a/CDF_Lid_Tolerance/SplineCDF_Fall2025_Lid Mat Cost.xlsx
+++ b/CDF_Lid_Tolerance/SplineCDF_Fall2025_Lid Mat Cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF_Lid_Tolerance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="354" documentId="13_ncr:1_{545E635C-8E76-4E81-96AA-7CE204948167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{886A31E0-1E34-4810-9603-5CE0FF79E901}"/>
+  <xr:revisionPtr revIDLastSave="1354" documentId="13_ncr:1_{545E635C-8E76-4E81-96AA-7CE204948167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBEE28E8-B0C2-4808-8127-678DEBFFDA5D}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6545,127 +6545,127 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>0.29224228801401098</v>
+        <v>0.109527141211783</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>0.41329796036377697</v>
+        <v>0.21984398296241464</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <f ca="1">INDIRECT("Computations!B"&amp;C2)</f>
-        <v>0.35000000000000003</v>
+        <v>0.21000000000000002</v>
       </c>
       <c r="E2">
         <f ca="1">INDIRECT("Computations!B"&amp;(C2+1))</f>
-        <v>0.42000000000000004</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="F2">
         <f ca="1">INDIRECT("Computations!S"&amp;C2)</f>
-        <v>2.5714285714285717E-2</v>
+        <v>-2.9890109890109873E-2</v>
       </c>
       <c r="G2">
         <f ca="1">INDIRECT("Computations!R"&amp;C2)</f>
-        <v>-2.5714285714285717E-2</v>
+        <v>4.8351648351648326E-2</v>
       </c>
       <c r="H2">
         <f ca="1">INDIRECT("Computations!Q"&amp;C2)</f>
-        <v>0.06</v>
+        <v>6.1538461538461535E-2</v>
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-5.2242288014010985E-2</v>
+        <v>-9.5271412117829968E-3</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>0.87070480023351648</v>
-      </c>
-      <c r="K2" t="e">
+        <v>0.1548160446914737</v>
+      </c>
+      <c r="K2">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L2" t="e">
+        <v>0.13952120046497016</v>
+      </c>
+      <c r="L2">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>#NUM!</v>
+        <v>0.13952120046497016</v>
       </c>
       <c r="M2">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
-        <v>1.9999999999999998</v>
+        <v>-2.9310841983852378</v>
       </c>
       <c r="N2">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>-1.327940830174501</v>
+        <v>-1.1049687836091335</v>
       </c>
       <c r="O2">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>0.73715300840743203</v>
-      </c>
-      <c r="P2" t="e">
+        <v>-0.62741620192159353</v>
+      </c>
+      <c r="P2">
         <f ca="1">SQRT(N2^2/4-O2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q2" t="e">
+        <v>0.96574075460718523</v>
+      </c>
+      <c r="Q2">
         <f ca="1">P2^(1/3)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="R2" t="e">
+        <v>0.98844730063287267</v>
+      </c>
+      <c r="R2">
         <f ca="1">ACOS(-N2/2/P2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="S2" t="e">
+        <v>0.96175241539393153</v>
+      </c>
+      <c r="S2">
         <f ca="1">-Q2</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="T2" t="e">
+        <v>-0.98844730063287267</v>
+      </c>
+      <c r="T2">
         <f ca="1">COS(R2/3)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="U2" t="e">
+        <v>0.9490515057171639</v>
+      </c>
+      <c r="U2">
         <f ca="1">SQRT(3)*SIN(R2/3)</f>
-        <v>#NUM!</v>
+        <v>0.54580556839221805</v>
       </c>
       <c r="V2">
         <f ca="1">-G2/F2/3</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="W2" t="e">
+        <v>0.53921568627450978</v>
+      </c>
+      <c r="W2">
         <f ca="1">2*Q2*T2+V2</f>
+        <v>2.4153904842498979</v>
+      </c>
+      <c r="X2">
+        <f ca="1">S2*(T2+U2)+V2</f>
+        <v>-0.93837175346086277</v>
+      </c>
+      <c r="Y2">
+        <f ca="1">S2*(T2-U2)+V2</f>
+        <v>0.14062832803449449</v>
+      </c>
+      <c r="Z2" t="e">
+        <f ca="1">-N2/2+SQRT(O2)</f>
         <v>#NUM!</v>
       </c>
-      <c r="X2" t="e">
-        <f ca="1">S2*(T2+U2)+V2</f>
+      <c r="AA2" t="e">
+        <f ca="1">Z2^(1/3)</f>
         <v>#NUM!</v>
       </c>
-      <c r="Y2" t="e">
-        <f ca="1">S2*(T2-U2)+V2</f>
+      <c r="AB2" t="e">
+        <f ca="1">-N2/2-SQRT(O2)</f>
         <v>#NUM!</v>
       </c>
-      <c r="Z2">
-        <f ca="1">-N2/2+SQRT(O2)</f>
-        <v>1.5225465668684608</v>
-      </c>
-      <c r="AA2">
-        <f ca="1">Z2^(1/3)</f>
-        <v>1.1504211606416055</v>
-      </c>
-      <c r="AB2">
-        <f ca="1">-N2/2-SQRT(O2)</f>
-        <v>-0.19460573669395986</v>
-      </c>
-      <c r="AC2">
+      <c r="AC2" t="e">
         <f ca="1">AB2^(1/3)</f>
-        <v>-0.57949791734955358</v>
-      </c>
-      <c r="AD2">
+        <v>#NUM!</v>
+      </c>
+      <c r="AD2" t="e">
         <f ca="1">AA2+AC2+V2</f>
-        <v>0.90425657662538517</v>
+        <v>#NUM!</v>
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>0.90425657662538517</v>
+        <v>0.14062832803449449</v>
       </c>
       <c r="AG2" t="s">
         <v>58</v>
@@ -36499,12 +36499,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -36646,15 +36643,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00701729-9E26-45E2-A33F-8BB46F87F68B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EF0FBCC-E871-4949-A77D-1C46D5FD7A0C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -36678,10 +36679,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EF0FBCC-E871-4949-A77D-1C46D5FD7A0C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00701729-9E26-45E2-A33F-8BB46F87F68B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>